--- a/バッチ・通知仕様書.xlsx
+++ b/バッチ・通知仕様書.xlsx
@@ -1605,8 +1605,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ReadingPlan モデルの deleting イベント
-ReadingPlanController@destroy</t>
+          <t>ReadingPlanController@destroy</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1621,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>書籍の読書計画はデータベースの連鎖削除（cascadeOnDelete）で削除されるが、モデルのイベントが呼ばれないため、通知は削除されずに残る（README「既知の課題」参照）。</t>
+          <t>書籍の読書計画はデータベースの連鎖削除（cascadeOnDelete）で削除されるが、ReadingPlanController@destroy を通らないため、通知は削除されずに残る（コーチ確認済み：書籍削除時の通知削除は対応不要。README「既知の課題」参照）。</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
